--- a/Models/CLIP/female1data/clip_big5_female1_short_hair.xlsx
+++ b/Models/CLIP/female1data/clip_big5_female1_short_hair.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucs-my.sharepoint.com/personal/yq_c_tamu_edu/Documents/Research/genderBias/GenderBias-SRL-Implementation/Models/CLIP/female1data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_ED8FB77A046D5DFB0637EA895BB1D38DEC6C75FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B378A3A-683F-4A28-9B23-89FBEA1B6F6A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="11820" windowHeight="10890" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Extraversion" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,25 @@
     <sheet name="Neuroticism" sheetId="4" r:id="rId4"/>
     <sheet name="Openness" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="48">
   <si>
     <t>Positive Trait</t>
   </si>
@@ -159,14 +178,25 @@
   </si>
   <si>
     <t>Likes to reflect, play with ideas</t>
+  </si>
+  <si>
+    <t>avg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -194,21 +224,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,7 +289,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -280,6 +323,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -314,9 +358,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,11 +534,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,62 +558,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.07573733478784561</v>
+        <v>7.5737334787845612E-2</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
       <c r="D2">
-        <v>0.01885448954999447</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1.8854489549994469E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.06874031573534012</v>
+        <v>6.8740315735340118E-2</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>0.003729212330654263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>3.7292123306542631E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.02860046178102493</v>
+        <v>2.8600461781024929E-2</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0.002912401687353849</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>2.912401687353849E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.02296433411538601</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>2.2964334115386009E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.01271197013556957</v>
+        <v>1.2711970135569571E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>4.175088331103325E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>8.4987011893341933E-3</v>
       </c>
     </row>
   </sheetData>
@@ -571,11 +635,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -589,68 +659,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.06133489310741425</v>
+        <v>6.1334893107414253E-2</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2">
-        <v>0.01601387187838554</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1.601387187838554E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.01326510682702065</v>
+        <v>1.326510682702065E-2</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3">
-        <v>0.01554123125970364</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.554123125970364E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.01130936667323112</v>
+        <v>1.130936667323112E-2</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>0.01382503099739552</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.3825030997395521E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.009322475641965866</v>
+        <v>9.3224756419658661E-3</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>0.007213296834379435</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>7.2132968343794346E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.005829674191772938</v>
+        <v>5.8296741917729378E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>2.0212303288280966E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>1.3148357742466034E-2</v>
       </c>
     </row>
   </sheetData>
@@ -659,11 +742,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -677,68 +764,81 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2">
-        <v>0.02921806089580059</v>
+        <v>2.9218060895800591E-2</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2">
-        <v>0.007191975135356188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>7.1919751353561878E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0.01301901135593653</v>
+        <v>1.3019011355936531E-2</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3">
-        <v>0.003529528621584177</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>3.529528621584177E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4">
-        <v>0.00586656155064702</v>
+        <v>5.8665615506470203E-3</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>0.002152477158233523</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>2.1524771582335229E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5">
-        <v>0.001943981740623713</v>
+        <v>1.943981740623713E-3</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
       </c>
       <c r="D5">
-        <v>0.001512716058641672</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>1.5127160586416719E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6">
-        <v>0.001507111708633602</v>
+        <v>1.5071117086336021E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>1.031094545032829E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>3.5966742434538901E-3</v>
       </c>
     </row>
   </sheetData>
@@ -747,11 +847,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -765,62 +869,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
       <c r="B2">
-        <v>0.05434208735823631</v>
+        <v>5.4342087358236313E-2</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0.01736758090555668</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1.7367580905556679E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3">
-        <v>0.031195979565382</v>
+        <v>3.1195979565382E-2</v>
       </c>
       <c r="C3" t="s">
         <v>34</v>
       </c>
       <c r="D3">
-        <v>0.01419808808714151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.419808808714151E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
       <c r="B4">
-        <v>0.01464705169200897</v>
+        <v>1.464705169200897E-2</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4">
-        <v>0.01118359994143248</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.118359994143248E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>0.005308393388986588</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>5.3083933889865884E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>37</v>
       </c>
       <c r="D6">
-        <v>0.004519298207014799</v>
+        <v>4.5192982070147991E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>3.3395039538542427E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>1.0515392106026412E-2</v>
       </c>
     </row>
   </sheetData>
@@ -829,11 +946,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="35.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -847,7 +968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -858,61 +979,74 @@
         <v>45</v>
       </c>
       <c r="D2">
-        <v>0.05645135045051575</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>5.6451350450515747E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
       <c r="B3">
-        <v>0.05502640455961227</v>
+        <v>5.5026404559612267E-2</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
       </c>
       <c r="D3">
-        <v>0.009918179363012314</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>9.9181793630123138E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4">
-        <v>0.05257370695471764</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>5.2573706954717643E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
       <c r="B5">
-        <v>0.03297743573784828</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>3.2977435737848282E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
       <c r="B6">
-        <v>0.0133707020431757</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>1.3370702043175701E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>43</v>
       </c>
       <c r="B7">
-        <v>0.004658293910324574</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>4.6582939103245744E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
       <c r="B8">
-        <v>0.00266256695613265</v>
+        <v>2.6625669561326499E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="1">
+        <f>AVERAGE(B2:B8)</f>
+        <v>4.6717362278806317E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <f>AVERAGE(D2:D8)</f>
+        <v>3.318476490676403E-2</v>
       </c>
     </row>
   </sheetData>
